--- a/artfynd/A 21223-2024 artfynd.xlsx
+++ b/artfynd/A 21223-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123460195</v>
+        <v>123460200</v>
       </c>
       <c r="B2" t="n">
-        <v>95916</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flytbäcken, Flytbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388110</v>
+        <v>388104</v>
       </c>
       <c r="R2" t="n">
-        <v>6612179</v>
+        <v>6612175</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,9 +752,19 @@
           <t>2025-03-25</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +779,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sofia Martinell-Funch</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sofia Martinell-Funch</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123460200</v>
+        <v>123460195</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>95922</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +803,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flytbäcken, Flytbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388104</v>
+        <v>388110</v>
       </c>
       <c r="R3" t="n">
-        <v>6612175</v>
+        <v>6612179</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,19 +864,9 @@
           <t>2025-03-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,12 +881,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sofia Martinell-Funch</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sofia Martinell-Funch</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 21223-2024 artfynd.xlsx
+++ b/artfynd/A 21223-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123460200</v>
+        <v>123460195</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
+        <v>95942</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flytbäcken, Flytbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388104</v>
+        <v>388110</v>
       </c>
       <c r="R2" t="n">
-        <v>6612175</v>
+        <v>6612179</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +748,9 @@
           <t>2025-03-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sofia Martinell-Funch</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sofia Martinell-Funch</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123460195</v>
+        <v>123460200</v>
       </c>
       <c r="B3" t="n">
-        <v>95925</v>
+        <v>98396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flytbäcken, Flytbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388110</v>
+        <v>388104</v>
       </c>
       <c r="R3" t="n">
-        <v>6612179</v>
+        <v>6612175</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,9 +854,19 @@
           <t>2025-03-25</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,12 +881,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sofia Martinell-Funch</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sofia Martinell-Funch</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 21223-2024 artfynd.xlsx
+++ b/artfynd/A 21223-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123460195</v>
       </c>
       <c r="B2" t="n">
-        <v>95942</v>
+        <v>95949</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>123460200</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 21223-2024 artfynd.xlsx
+++ b/artfynd/A 21223-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123460195</v>
       </c>
       <c r="B2" t="n">
-        <v>95949</v>
+        <v>95951</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>123460200</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 21223-2024 artfynd.xlsx
+++ b/artfynd/A 21223-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123460195</v>
+        <v>123460200</v>
       </c>
       <c r="B2" t="n">
-        <v>95951</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flytbäcken, Flytbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388110</v>
+        <v>388104</v>
       </c>
       <c r="R2" t="n">
-        <v>6612179</v>
+        <v>6612175</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,9 +752,19 @@
           <t>2025-03-25</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +779,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sofia Martinell-Funch</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sofia Martinell-Funch</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123460200</v>
+        <v>123460195</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>96332</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +803,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flytbäcken, Flytbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388104</v>
+        <v>388110</v>
       </c>
       <c r="R3" t="n">
-        <v>6612175</v>
+        <v>6612179</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,19 +864,9 @@
           <t>2025-03-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,12 +881,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sofia Martinell-Funch</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sofia Martinell-Funch</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 21223-2024 artfynd.xlsx
+++ b/artfynd/A 21223-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123460200</v>
+        <v>123460195</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
+        <v>96332</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flytbäcken, Flytbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388104</v>
+        <v>388110</v>
       </c>
       <c r="R2" t="n">
-        <v>6612175</v>
+        <v>6612179</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +748,9 @@
           <t>2025-03-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sofia Martinell-Funch</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sofia Martinell-Funch</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123460195</v>
+        <v>123460200</v>
       </c>
       <c r="B3" t="n">
-        <v>96332</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flytbäcken, Flytbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388110</v>
+        <v>388104</v>
       </c>
       <c r="R3" t="n">
-        <v>6612179</v>
+        <v>6612175</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,9 +854,19 @@
           <t>2025-03-25</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,12 +881,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sofia Martinell-Funch</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sofia Martinell-Funch</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 21223-2024 artfynd.xlsx
+++ b/artfynd/A 21223-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123460195</v>
+        <v>123460200</v>
       </c>
       <c r="B2" t="n">
-        <v>96332</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flytbäcken, Flytbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388110</v>
+        <v>388104</v>
       </c>
       <c r="R2" t="n">
-        <v>6612179</v>
+        <v>6612175</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,9 +752,19 @@
           <t>2025-03-25</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +779,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sofia Martinell-Funch</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sofia Martinell-Funch</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123460200</v>
+        <v>123460195</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
+        <v>96332</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +803,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flytbäcken, Flytbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388104</v>
+        <v>388110</v>
       </c>
       <c r="R3" t="n">
-        <v>6612175</v>
+        <v>6612179</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,19 +864,9 @@
           <t>2025-03-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,12 +881,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sofia Martinell-Funch</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sofia Martinell-Funch</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 21223-2024 artfynd.xlsx
+++ b/artfynd/A 21223-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,6 +891,117 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125684773</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>388106</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6612181</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21223-2024 artfynd.xlsx
+++ b/artfynd/A 21223-2024 artfynd.xlsx
@@ -896,12 +896,7 @@
         <v>125684773</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21223-2024 artfynd.xlsx
+++ b/artfynd/A 21223-2024 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>125684773</v>
       </c>
       <c r="B4" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21223-2024 artfynd.xlsx
+++ b/artfynd/A 21223-2024 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>125684773</v>
       </c>
       <c r="B4" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21223-2024 artfynd.xlsx
+++ b/artfynd/A 21223-2024 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>125684773</v>
       </c>
       <c r="B4" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21223-2024 artfynd.xlsx
+++ b/artfynd/A 21223-2024 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>125684773</v>
       </c>
       <c r="B4" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21223-2024 artfynd.xlsx
+++ b/artfynd/A 21223-2024 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>125684773</v>
       </c>
       <c r="B4" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21223-2024 artfynd.xlsx
+++ b/artfynd/A 21223-2024 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>125684773</v>
       </c>
       <c r="B4" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21223-2024 artfynd.xlsx
+++ b/artfynd/A 21223-2024 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>125684773</v>
       </c>
       <c r="B4" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21223-2024 artfynd.xlsx
+++ b/artfynd/A 21223-2024 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>125684773</v>
       </c>
       <c r="B4" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21223-2024 artfynd.xlsx
+++ b/artfynd/A 21223-2024 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>125684773</v>
       </c>
       <c r="B4" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
